--- a/data/trans_bre/P3A_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -612,42 +612,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>39,93</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,11</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>19,76</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>20,49</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>101,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,12; 45,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,6; 40,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,49; 25,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,8; 25,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>76,34; 131,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,96; 85,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,95; 39,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,04; 37,1</t>
         </is>
       </c>
     </row>
@@ -712,42 +712,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>36,79</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,76</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>28,19</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>24,69</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,57; 42,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,87; 41,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,7; 34,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,81; 30,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>57,19; 101,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,8; 83,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,31; 56,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,1; 46,42</t>
         </is>
       </c>
     </row>
@@ -812,42 +812,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>54,02</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>38,45</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>35,86</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>49,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>158,42%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>116,44%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,22; 60,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31,9; 44,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,84; 41,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,94; 74,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>125,27; 195,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,96; 100,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,47; 81,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34,17; 433,12</t>
         </is>
       </c>
     </row>
@@ -912,42 +912,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>52,99</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>45,6</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>36,75</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>28,37</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>159,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>104,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>49,25; 56,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,6; 49,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,3; 40,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,41; 33,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>139,72; 183,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,17; 121,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>59,48; 80,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,15; 51,05</t>
         </is>
       </c>
     </row>
@@ -1012,42 +1012,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>54,97</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>46,6</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>45,39</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>153,77%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>115,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,51%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,36; 60,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,38; 51,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,35; 49,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,58; 37,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>115,6; 196,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>94,03; 143,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>80,32; 115,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,45; 66,09</t>
         </is>
       </c>
     </row>
@@ -1112,42 +1112,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>68,75</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>60,91</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>54,76</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>33,59</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>583,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>442,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>218,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64,22; 72,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>55,34; 65,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,79; 60,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,37; 45,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>400,68; 830,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>301,34; 660,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>161,0; 296,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,49; 124,7</t>
         </is>
       </c>
     </row>
@@ -1212,42 +1212,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>49,94</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>39,83</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,26</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>30,39</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>146,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,71%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,68; 51,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,74; 41,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,28; 36,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,03; 46,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>133,71; 159,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>83,26; 99,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>59,28; 70,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,78; 104,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,49</t>
+          <t>20,86</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,12; 45,99</t>
+          <t>33,13; 46,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,6; 40,03</t>
+          <t>27,88; 40,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,49; 25,38</t>
+          <t>13,23; 25,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,8; 25,26</t>
+          <t>16,26; 25,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,34; 131,12</t>
+          <t>77,16; 134,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,96; 85,48</t>
+          <t>50,57; 87,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,95; 39,95</t>
+          <t>18,6; 39,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,04; 37,1</t>
+          <t>21,91; 37,47</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24,69</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,57; 42,82</t>
+          <t>29,62; 43,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,87; 41,02</t>
+          <t>27,96; 41,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,7; 34,08</t>
+          <t>22,96; 34,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,81; 30,11</t>
+          <t>19,18; 29,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>57,19; 101,17</t>
+          <t>57,54; 103,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,8; 83,18</t>
+          <t>47,06; 83,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,31; 56,63</t>
+          <t>33,2; 56,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,1; 46,42</t>
+          <t>26,17; 45,5</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49,06</t>
+          <t>26,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>116,44%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47,22; 60,3</t>
+          <t>46,27; 59,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,9; 44,16</t>
+          <t>32,34; 44,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,84; 41,82</t>
+          <t>28,43; 41,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,94; 74,03</t>
+          <t>18,45; 31,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>125,27; 195,04</t>
+          <t>125,31; 193,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,96; 100,09</t>
+          <t>65,1; 102,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,47; 81,43</t>
+          <t>48,71; 80,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,17; 433,12</t>
+          <t>26,96; 51,41</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28,37</t>
+          <t>28,03</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49,25; 56,67</t>
+          <t>48,97; 56,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,6; 49,56</t>
+          <t>41,69; 49,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,3; 40,52</t>
+          <t>33,22; 40,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,41; 33,28</t>
+          <t>24,87; 31,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>139,72; 183,18</t>
+          <t>138,51; 183,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,17; 121,32</t>
+          <t>89,85; 119,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,48; 80,03</t>
+          <t>59,85; 79,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,15; 51,05</t>
+          <t>35,81; 50,19</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>31,47</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>48,36; 60,78</t>
+          <t>49,39; 60,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,38; 51,53</t>
+          <t>41,99; 51,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,35; 49,62</t>
+          <t>40,7; 50,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,58; 37,92</t>
+          <t>26,9; 35,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>115,6; 196,42</t>
+          <t>122,03; 197,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,03; 143,13</t>
+          <t>95,71; 145,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,32; 115,8</t>
+          <t>81,41; 118,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,45; 66,09</t>
+          <t>40,49; 61,81</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33,59</t>
+          <t>36,43</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64,22; 72,7</t>
+          <t>63,35; 72,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55,34; 65,28</t>
+          <t>55,3; 65,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,79; 60,26</t>
+          <t>48,37; 60,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,37; 45,54</t>
+          <t>25,46; 47,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>400,68; 830,91</t>
+          <t>380,73; 865,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>301,34; 660,82</t>
+          <t>296,24; 635,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>161,0; 296,35</t>
+          <t>157,47; 305,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40,49; 124,7</t>
+          <t>46,92; 139,27</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30,39</t>
+          <t>25,41</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>47,68; 51,99</t>
+          <t>47,74; 51,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,74; 41,97</t>
+          <t>37,7; 41,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,28; 36,37</t>
+          <t>32,03; 36,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,03; 46,91</t>
+          <t>23,43; 27,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>133,71; 159,32</t>
+          <t>132,94; 158,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,26; 99,48</t>
+          <t>83,39; 99,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,28; 70,46</t>
+          <t>58,41; 70,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,78; 104,36</t>
+          <t>34,78; 43,02</t>
         </is>
       </c>
     </row>
